--- a/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Martinelli's Apple Juice Squat</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.85</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>La Colombe - Vanilla</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>35.45</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35.45</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.45</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Remedy - Superseed Fuel</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Remedy - Matcha Fuel</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25.06</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Remedy - Berry Immunity</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.06</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Harmless Harvest - Coconut Water</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>65.48</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>65.48</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="E7" t="n">
+        <v>65.48</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Simply Gum - Peppermints</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.27</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Bob's Bar - Oat, PB Coconut</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>15.69</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>15.69</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15.69</v>
       </c>
     </row>
   </sheetData>
